--- a/ExportedReports/Tasks_Sarah_Connor_Only.xlsx
+++ b/ExportedReports/Tasks_Sarah_Connor_Only.xlsx
@@ -19,7 +19,7 @@
     <x:t>Task Management System — Export Report</x:t>
   </x:si>
   <x:si>
-    <x:t>Filters: User: Sarah Connor | Exported: 2026-10-21 02:32 UTC | Total: 5</x:t>
+    <x:t>Filters: User: Sarah Connor | Exported: 2026-10-21 05:50 AM (Egypt Time) | Total: 5</x:t>
   </x:si>
   <x:si>
     <x:t>Task #</x:t>
@@ -46,46 +46,46 @@
     <x:t>sarah.connor@tasksystem.com</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-10-20 23:32</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-10-21 00:32</x:t>
+    <x:t>2026-10-21 02:32 AM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-10-21 03:32 AM</x:t>
   </x:si>
   <x:si>
     <x:t>[Flutter Task Submission UI] Designed and developed the Flutter form screen allowing employees to enter task descriptions, select completed timestamps, and submit to the backend API.</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-10-19 02:32</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-10-19 03:32</x:t>
+    <x:t>2026-10-19 05:32 AM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-10-19 06:32 AM</x:t>
   </x:si>
   <x:si>
     <x:t>[Secure JWT Storage in Flutter] Integrated flutter_secure_storage package to store authentication tokens and automatically attach Authorization Bearer headers to HTTP interceptors.</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-10-16 02:32</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-10-16 04:32</x:t>
+    <x:t>2026-10-16 05:32 AM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-10-16 07:32 AM</x:t>
   </x:si>
   <x:si>
     <x:t>[State Management with Bloc] Refactored user task history view to use flutter_bloc. Handled loading, loaded, and network failure states with custom retry widgets.</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-10-03 02:32</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-10-03 03:17</x:t>
+    <x:t>2026-10-03 05:32 AM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-10-03 06:17 AM</x:t>
   </x:si>
   <x:si>
     <x:t>[Offline Task Sync Service] Added SQLite local database caching so employees can log tasks even while offline and batch-sync them once network connection restores.</x:t>
   </x:si>
   <x:si>
-    <x:t>2026-08-07 02:32</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-08-07 05:32</x:t>
+    <x:t>2026-08-07 05:32 AM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-08-07 08:32 AM</x:t>
   </x:si>
   <x:si>
     <x:t>[Android &amp; iOS App Signing] Configured keystores, provisioning profiles, and automated Fastlane pipelines for staging deployment builds.</x:t>
@@ -619,7 +619,8 @@
   <x:cols>
     <x:col min="1" max="1" width="10.710625" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="24.710625" style="0" customWidth="1"/>
-    <x:col min="3" max="5" width="28.710625" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="28.710625" style="0" customWidth="1"/>
+    <x:col min="4" max="5" width="30.710625" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="50.710625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
